--- a/livrables/Chiffrage_Couts_Rentabilite.xlsx
+++ b/livrables/Chiffrage_Couts_Rentabilite.xlsx
@@ -96,7 +96,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -113,6 +113,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -731,7 +734,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C37"/>
+  <dimension ref="A1:C40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -754,12 +757,14 @@
           <t>Durée d'un sprint (semaines)</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>2</v>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2 (Sprint 3 : 3)</t>
+        </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Démarche SCRUM, 2 semaines par sprint</t>
+          <t>Sprint 3 étendu à 3 semaines : 60 j de charge ne tiennent pas sur 10 j ouvrés (2 sem.) sans mobiliser 6 personnes à temps plein en simultané</t>
         </is>
       </c>
     </row>
@@ -781,15 +786,15 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Durée totale du projet (mois)</t>
+          <t>Durée totale du projet (semaines)</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>≈ 12 semaines de développement</t>
+          <t>5 sprints × 2 semaines + Sprint 3 × 3 semaines</t>
         </is>
       </c>
     </row>
@@ -994,7 +999,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Azure Machine Learning (compute GPU entraînement)</t>
+          <t>Azure Machine Learning (compute GPU entraînement, NC6s v3)</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1002,7 +1007,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>≈ 200h GPU NC6 sur la phase</t>
+          <t>≈ 2000h GPU cumulées sur 3 mois (usage quasi continu : itérations + hyperparameter tuning). NC6s v3 ≈ 3,8 €/h — le SKU 'NC6' d'origine est retiré du catalogue Azure</t>
         </is>
       </c>
     </row>
@@ -1039,7 +1044,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Sécurité &amp; monitoring (Defender, Sentinel)</t>
+          <t>Sécurité &amp; monitoring (Microsoft Defender for Cloud)</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -1047,7 +1052,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sur la phase projet</t>
+          <t>Sur la phase projet, sans SIEM Sentinel (coût prohibitif pour ce périmètre, cf. onglet prod)</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1078,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Hébergement API recommandation (App Service + AKS)</t>
+          <t>Hébergement API recommandation (Azure App Service, auto-scaling)</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1081,14 +1086,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Auto-scaling, charge moyenne</t>
+          <t>Variable — charge moyenne à 50k utilisateurs actifs (An 1)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Inférence ML (Azure ML Endpoint)</t>
+          <t>Inférence ML (Azure ML Endpoint, CPU + cache embeddings, scale-to-zero)</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -1096,7 +1101,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>≈ 1M requêtes/mois</t>
+          <t>Variable — ≈ 1M requêtes/mois à 50k utilisateurs actifs (An 1). Suppose une inférence CPU (embeddings pré-calculés) ; si un modèle GPU temps réel s'avère nécessaire, ce poste serait à revoir nettement à la hausse (un seul GPU NC6s v3 24/7 coûte à lui seul ≈ 31 000€/an)</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1116,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Chiffré, redondance ZRS</t>
+          <t>Variable — chiffré, redondance ZRS, à 50k utilisateurs actifs (An 1)</t>
         </is>
       </c>
     </row>
@@ -1126,131 +1131,174 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Compte utilisateur + préférences</t>
+          <t>Fixe — compte utilisateur + préférences</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Sécurité, sauvegarde, monitoring</t>
+          <t>Sécurité, sauvegarde, monitoring (Defender + Azure Monitor)</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Defender, alerting, backups</t>
+          <t>Fixe — sans SIEM Sentinel : à 5,59 $/Go analysé, Sentinel dépasserait ce budget avec quelques dizaines de Go/mois ingérés</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>Total Azure annuel (€)</t>
+          <t>Total Azure annuel (€, base An 1 à 50k utilisateurs)</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>40000</v>
+        <v>39000</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="inlineStr">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Note : les postes variables sont indexés sur √(utilisateurs actifs / 50 000) d'une année sur l'autre</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr"/>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Hypothèse d'économies d'échelle — évite une croissance linéaire irréaliste des coûts cloud ; détail par année dans l'onglet Rentabilité</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
         <is>
           <t>Hypothèses gains marketing</t>
         </is>
       </c>
-      <c r="B31" s="1" t="n"/>
-      <c r="C31" s="1" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Nb utilisateurs actifs an 1</t>
-        </is>
-      </c>
-      <c r="B32" t="n">
-        <v>50000</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Lancement progressif</t>
-        </is>
-      </c>
+      <c r="B32" s="1" t="n"/>
+      <c r="C32" s="1" t="n"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Nb utilisateurs actifs an 2</t>
+          <t>Nb utilisateurs actifs an 1</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>150000</v>
+        <v>50000</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Marketing &amp; bouche à oreille</t>
+          <t>Lancement progressif</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Nb utilisateurs actifs an 3</t>
+          <t>Nb utilisateurs actifs an 2</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>280000</v>
+        <v>150000</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Croissance maintenue</t>
+          <t>Marketing &amp; bouche à oreille</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Nb utilisateurs actifs an 4</t>
+          <t>Nb utilisateurs actifs an 3</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>380000</v>
+        <v>280000</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Plafonnement</t>
+          <t>Croissance maintenue</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Nb utilisateurs actifs an 5</t>
+          <t>Nb utilisateurs actifs an 4</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>450000</v>
+        <v>380000</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Maturité</t>
+          <t>Plafonnement</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Panier moyen induit / utilisateur / an (€)</t>
+          <t>Nb utilisateurs actifs an 5</t>
         </is>
       </c>
       <c r="B37" t="n">
+        <v>450000</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Maturité</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Taux de conversion recommandation → achat</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Part des utilisateurs actifs générant réellement un panier additionnel via la reco (aligné avec le KPI cible ≥5%, cf. présentation COMEX) — un utilisateur actif n'est pas un acheteur</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Panier additionnel moyen / utilisateur convertissant / an (€)</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
         <v>25</v>
       </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Upsell estimé par le marketing</t>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Upsell estimé par le marketing, appliqué uniquement aux utilisateurs qui convertissent</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Marge brute retail moyenne</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Pour convertir le CA additionnel en gain net comparable aux coûts (le panier ci-dessus est du CA, pas du profit)</t>
         </is>
       </c>
     </row>
@@ -1500,11 +1548,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="55" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1515,7 +1564,12 @@
       </c>
       <c r="B1" s="3" t="inlineStr">
         <is>
-          <t>Montant annuel (€)</t>
+          <t>Montant annuel (€, base An 1)</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Type</t>
         </is>
       </c>
     </row>
@@ -1528,48 +1582,94 @@
       <c r="B2" s="5" t="n">
         <v>19092</v>
       </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Fixe</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>Infrastructure Azure production</t>
+          <t>Infrastructure Azure — hébergement/inférence/stockage</t>
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>40000</v>
+        <v>32000</v>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Variable (usagers)</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>Ré-entraînement modèles (compute + DS junior 20j)</t>
+          <t>Infrastructure Azure — BDD, sécurité &amp; monitoring</t>
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>18000</v>
+        <v>7000</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>Fixe</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
+          <t>Ré-entraînement modèles (compute + DS junior 20j)</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>18000</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Fixe</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
           <t>DPO / RGPD - veille et audits</t>
         </is>
       </c>
-      <c r="B5" s="5" t="n">
+      <c r="B6" s="5" t="n">
         <v>6000</v>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>TOTAL annuel (€)</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="n">
-        <v>83092</v>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Fixe</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>TOTAL annuel (€, base An 1 à 50k utilisateurs)</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>82092</v>
+      </c>
+      <c r="C7" s="7" t="n"/>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>Le poste 'Variable (usagers)' croît avec le nombre d'utilisateurs actifs (facteur √(utilisateurs / 50 000)) — voir la progression année par année dans l'onglet Rentabilité.</t>
+        </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A9:C9"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1580,7 +1680,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -1630,152 +1730,166 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="8" t="inlineStr">
+      <c r="A2" s="9" t="inlineStr">
         <is>
           <t>Coûts (initial / annuels)</t>
         </is>
       </c>
-      <c r="B2" s="9" t="n">
+      <c r="B2" s="10" t="n">
         <v>141280</v>
       </c>
-      <c r="C2" s="9" t="n">
-        <v>83092</v>
-      </c>
-      <c r="D2" s="9" t="n">
-        <v>83092</v>
-      </c>
-      <c r="E2" s="9" t="n">
-        <v>83092</v>
-      </c>
-      <c r="F2" s="9" t="n">
-        <v>83092</v>
-      </c>
-      <c r="G2" s="9" t="n">
-        <v>83092</v>
+      <c r="C2" s="10" t="n">
+        <v>82092</v>
+      </c>
+      <c r="D2" s="10" t="n">
+        <v>105518</v>
+      </c>
+      <c r="E2" s="10" t="n">
+        <v>125818</v>
+      </c>
+      <c r="F2" s="10" t="n">
+        <v>138310</v>
+      </c>
+      <c r="G2" s="10" t="n">
+        <v>146092</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="8" t="inlineStr">
+      <c r="A3" s="9" t="inlineStr">
         <is>
           <t>Coûts cumulés</t>
         </is>
       </c>
-      <c r="B3" s="9">
+      <c r="B3" s="10">
         <f>B2</f>
         <v/>
       </c>
-      <c r="C3" s="9">
+      <c r="C3" s="10">
         <f>B3+C2</f>
         <v/>
       </c>
-      <c r="D3" s="9">
+      <c r="D3" s="10">
         <f>C3+D2</f>
         <v/>
       </c>
-      <c r="E3" s="9">
+      <c r="E3" s="10">
         <f>D3+E2</f>
         <v/>
       </c>
-      <c r="F3" s="9">
+      <c r="F3" s="10">
         <f>E3+F2</f>
         <v/>
       </c>
-      <c r="G3" s="9">
+      <c r="G3" s="10">
         <f>F3+G2</f>
         <v/>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="inlineStr">
+      <c r="A4" s="9" t="inlineStr">
         <is>
           <t>Gains annuels</t>
         </is>
       </c>
-      <c r="B4" s="9" t="n">
+      <c r="B4" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="C4" s="9" t="n">
-        <v>1250000</v>
-      </c>
-      <c r="D4" s="9" t="n">
-        <v>3750000</v>
-      </c>
-      <c r="E4" s="9" t="n">
-        <v>7000000</v>
-      </c>
-      <c r="F4" s="9" t="n">
-        <v>9500000</v>
-      </c>
-      <c r="G4" s="9" t="n">
-        <v>11250000</v>
+      <c r="C4" s="10" t="n">
+        <v>45000</v>
+      </c>
+      <c r="D4" s="10" t="n">
+        <v>135000</v>
+      </c>
+      <c r="E4" s="10" t="n">
+        <v>252000</v>
+      </c>
+      <c r="F4" s="10" t="n">
+        <v>342000</v>
+      </c>
+      <c r="G4" s="10" t="n">
+        <v>405000</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="inlineStr">
+      <c r="A5" s="9" t="inlineStr">
         <is>
           <t>Gains cumulés</t>
         </is>
       </c>
-      <c r="B5" s="9">
+      <c r="B5" s="10">
         <f>B4</f>
         <v/>
       </c>
-      <c r="C5" s="9">
+      <c r="C5" s="10">
         <f>B5+C4</f>
         <v/>
       </c>
-      <c r="D5" s="9">
+      <c r="D5" s="10">
         <f>C5+D4</f>
         <v/>
       </c>
-      <c r="E5" s="9">
+      <c r="E5" s="10">
         <f>D5+E4</f>
         <v/>
       </c>
-      <c r="F5" s="9">
+      <c r="F5" s="10">
         <f>E5+F4</f>
         <v/>
       </c>
-      <c r="G5" s="9">
+      <c r="G5" s="10">
         <f>F5+G4</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>Solde cumulé (gains - coûts)</t>
         </is>
       </c>
-      <c r="B6" s="11">
+      <c r="B6" s="12">
         <f>B5-B3</f>
         <v/>
       </c>
-      <c r="C6" s="11">
+      <c r="C6" s="12">
         <f>C5-C3</f>
         <v/>
       </c>
-      <c r="D6" s="11">
+      <c r="D6" s="12">
         <f>D5-D3</f>
         <v/>
       </c>
-      <c r="E6" s="11">
+      <c r="E6" s="12">
         <f>E5-E3</f>
         <v/>
       </c>
-      <c r="F6" s="11">
+      <c r="F6" s="12">
         <f>F5-F3</f>
         <v/>
       </c>
-      <c r="G6" s="11">
+      <c r="G6" s="12">
         <f>G5-G3</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="12" t="inlineStr">
+      <c r="A28" s="13" t="inlineStr">
         <is>
           <t>Lecture : le projet devient rentable l'année où le 'Solde cumulé' devient positif.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="13" t="inlineStr">
+        <is>
+          <t>Gains = utilisateurs actifs × taux de conversion (8%) × panier additionnel (25€) × marge brute (45%) — pas 100% des utilisateurs actifs, et en gain net, pas en CA brut.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="13" t="inlineStr">
+        <is>
+          <t>Coûts annuels = socle fixe + coûts Azure variables indexés sur √(utilisateurs actifs / 50 000).</t>
         </is>
       </c>
     </row>
